--- a/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{268B4D59-649B-4EA6-8AEA-4E15BB603C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{035AFFC9-D1D7-4C9C-94E1-698E906EB546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3719,7 +3719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCC7686-D804-4D83-9A7F-69A13B5FC056}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5B1DA4-EAED-408C-95AB-40B8B15A4407}">
   <dimension ref="B9:E432"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{035AFFC9-D1D7-4C9C-94E1-698E906EB546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{595C2AE0-DC5F-478F-998F-850D0C68C50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3719,7 +3719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5B1DA4-EAED-408C-95AB-40B8B15A4407}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFA9854-6934-4FBD-8983-99D635CE5E0F}">
   <dimension ref="B9:E432"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{595C2AE0-DC5F-478F-998F-850D0C68C50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4192FBC4-3BB0-4BF9-9EDF-5AD7A54ED161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="480">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -349,69 +349,15 @@
     <t>t_pos_andor</t>
   </si>
   <si>
-    <t>p_w43843800</t>
-  </si>
-  <si>
-    <t>e_w43843800*</t>
+    <t>p_w173670759</t>
+  </si>
+  <si>
+    <t>e_w173670759*</t>
   </si>
   <si>
     <t>OR</t>
   </si>
   <si>
-    <t>p_w93235592</t>
-  </si>
-  <si>
-    <t>e_w93235592*</t>
-  </si>
-  <si>
-    <t>p_w107574175</t>
-  </si>
-  <si>
-    <t>e_w107574175*</t>
-  </si>
-  <si>
-    <t>p_w107614291</t>
-  </si>
-  <si>
-    <t>e_w107614291*</t>
-  </si>
-  <si>
-    <t>p_w107649691</t>
-  </si>
-  <si>
-    <t>e_w107649691*</t>
-  </si>
-  <si>
-    <t>p_w107655510</t>
-  </si>
-  <si>
-    <t>e_w107655510*</t>
-  </si>
-  <si>
-    <t>p_w172698243</t>
-  </si>
-  <si>
-    <t>e_w172698243*</t>
-  </si>
-  <si>
-    <t>p_w173534563</t>
-  </si>
-  <si>
-    <t>e_w173534563*</t>
-  </si>
-  <si>
-    <t>p_w173670736</t>
-  </si>
-  <si>
-    <t>e_w173670736*</t>
-  </si>
-  <si>
-    <t>p_w173670759</t>
-  </si>
-  <si>
-    <t>e_w173670759*</t>
-  </si>
-  <si>
     <t>p_w173677993</t>
   </si>
   <si>
@@ -424,96 +370,12 @@
     <t>e_w173682343*</t>
   </si>
   <si>
-    <t>p_w173805804</t>
-  </si>
-  <si>
-    <t>e_w173805804*</t>
-  </si>
-  <si>
-    <t>p_w173808767</t>
-  </si>
-  <si>
-    <t>e_w173808767*</t>
-  </si>
-  <si>
-    <t>p_w173985842</t>
-  </si>
-  <si>
-    <t>e_w173985842*</t>
-  </si>
-  <si>
-    <t>p_w174171686</t>
-  </si>
-  <si>
-    <t>e_w174171686*</t>
-  </si>
-  <si>
-    <t>p_w174171691</t>
-  </si>
-  <si>
-    <t>e_w174171691*</t>
-  </si>
-  <si>
-    <t>p_w174338940</t>
-  </si>
-  <si>
-    <t>e_w174338940*</t>
-  </si>
-  <si>
-    <t>p_w174342293</t>
-  </si>
-  <si>
-    <t>e_w174342293*</t>
-  </si>
-  <si>
-    <t>p_w174342295</t>
-  </si>
-  <si>
-    <t>e_w174342295*</t>
-  </si>
-  <si>
-    <t>p_w174347010</t>
-  </si>
-  <si>
-    <t>e_w174347010*</t>
-  </si>
-  <si>
-    <t>p_w174419698</t>
-  </si>
-  <si>
-    <t>e_w174419698*</t>
-  </si>
-  <si>
     <t>p_w174512286</t>
   </si>
   <si>
     <t>e_w174512286*</t>
   </si>
   <si>
-    <t>p_w175176155</t>
-  </si>
-  <si>
-    <t>e_w175176155*</t>
-  </si>
-  <si>
-    <t>p_w175299043</t>
-  </si>
-  <si>
-    <t>e_w175299043*</t>
-  </si>
-  <si>
-    <t>p_w175343993</t>
-  </si>
-  <si>
-    <t>e_w175343993*</t>
-  </si>
-  <si>
-    <t>p_w176684982</t>
-  </si>
-  <si>
-    <t>e_w176684982*</t>
-  </si>
-  <si>
     <t>p_w176932212</t>
   </si>
   <si>
@@ -532,78 +394,6 @@
     <t>e_w177004931*</t>
   </si>
   <si>
-    <t>p_w177011339</t>
-  </si>
-  <si>
-    <t>e_w177011339*</t>
-  </si>
-  <si>
-    <t>p_w206847211</t>
-  </si>
-  <si>
-    <t>e_w206847211*</t>
-  </si>
-  <si>
-    <t>p_w217926708</t>
-  </si>
-  <si>
-    <t>e_w217926708*</t>
-  </si>
-  <si>
-    <t>p_w217926710</t>
-  </si>
-  <si>
-    <t>e_w217926710*</t>
-  </si>
-  <si>
-    <t>p_w217926711</t>
-  </si>
-  <si>
-    <t>e_w217926711*</t>
-  </si>
-  <si>
-    <t>p_w217930454</t>
-  </si>
-  <si>
-    <t>e_w217930454*</t>
-  </si>
-  <si>
-    <t>p_w217933343</t>
-  </si>
-  <si>
-    <t>e_w217933343*</t>
-  </si>
-  <si>
-    <t>p_w217933346</t>
-  </si>
-  <si>
-    <t>e_w217933346*</t>
-  </si>
-  <si>
-    <t>p_w217941443</t>
-  </si>
-  <si>
-    <t>e_w217941443*</t>
-  </si>
-  <si>
-    <t>p_w217970970</t>
-  </si>
-  <si>
-    <t>e_w217970970*</t>
-  </si>
-  <si>
-    <t>p_w217976993</t>
-  </si>
-  <si>
-    <t>e_w217976993*</t>
-  </si>
-  <si>
-    <t>p_w218114438</t>
-  </si>
-  <si>
-    <t>e_w218114438*</t>
-  </si>
-  <si>
     <t>p_w221085150</t>
   </si>
   <si>
@@ -616,256 +406,64 @@
     <t>e_w226392269*</t>
   </si>
   <si>
-    <t>p_w226879630</t>
-  </si>
-  <si>
-    <t>e_w226879630*</t>
-  </si>
-  <si>
-    <t>p_w226886714</t>
-  </si>
-  <si>
-    <t>e_w226886714*</t>
-  </si>
-  <si>
     <t>p_w226912498</t>
   </si>
   <si>
     <t>e_w226912498*</t>
   </si>
   <si>
-    <t>p_w226918874</t>
-  </si>
-  <si>
-    <t>e_w226918874*</t>
-  </si>
-  <si>
-    <t>p_w226922540</t>
-  </si>
-  <si>
-    <t>e_w226922540*</t>
-  </si>
-  <si>
-    <t>p_w226985195</t>
-  </si>
-  <si>
-    <t>e_w226985195*</t>
-  </si>
-  <si>
-    <t>p_w227962923</t>
-  </si>
-  <si>
-    <t>e_w227962923*</t>
-  </si>
-  <si>
-    <t>p_w254853839</t>
-  </si>
-  <si>
-    <t>e_w254853839*</t>
-  </si>
-  <si>
-    <t>p_w261824495</t>
-  </si>
-  <si>
-    <t>e_w261824495*</t>
-  </si>
-  <si>
-    <t>p_w261824497</t>
-  </si>
-  <si>
-    <t>e_w261824497*</t>
-  </si>
-  <si>
-    <t>p_w262778513</t>
-  </si>
-  <si>
-    <t>e_w262778513*</t>
-  </si>
-  <si>
-    <t>p_w262778514</t>
-  </si>
-  <si>
-    <t>e_w262778514*</t>
-  </si>
-  <si>
-    <t>p_w262778515</t>
-  </si>
-  <si>
-    <t>e_w262778515*</t>
-  </si>
-  <si>
-    <t>p_w263135249</t>
-  </si>
-  <si>
-    <t>e_w263135249*</t>
-  </si>
-  <si>
-    <t>p_w292110924</t>
-  </si>
-  <si>
-    <t>e_w292110924*</t>
-  </si>
-  <si>
-    <t>p_w292487199</t>
-  </si>
-  <si>
-    <t>e_w292487199*</t>
-  </si>
-  <si>
-    <t>p_w293224489</t>
-  </si>
-  <si>
-    <t>e_w293224489*</t>
-  </si>
-  <si>
-    <t>p_w293467436</t>
-  </si>
-  <si>
-    <t>e_w293467436*</t>
-  </si>
-  <si>
-    <t>p_w294673631</t>
-  </si>
-  <si>
-    <t>e_w294673631*</t>
-  </si>
-  <si>
-    <t>p_w295277014</t>
-  </si>
-  <si>
-    <t>e_w295277014*</t>
-  </si>
-  <si>
-    <t>p_w310510674</t>
-  </si>
-  <si>
-    <t>e_w310510674*</t>
-  </si>
-  <si>
-    <t>p_w312609390</t>
-  </si>
-  <si>
-    <t>e_w312609390*</t>
-  </si>
-  <si>
-    <t>p_w317645604</t>
-  </si>
-  <si>
-    <t>e_w317645604*</t>
-  </si>
-  <si>
-    <t>p_w317645796</t>
-  </si>
-  <si>
-    <t>e_w317645796*</t>
-  </si>
-  <si>
-    <t>p_w340227647</t>
-  </si>
-  <si>
-    <t>e_w340227647*</t>
-  </si>
-  <si>
     <t>p_w359380463</t>
   </si>
   <si>
     <t>e_w359380463*</t>
   </si>
   <si>
-    <t>p_w364421786</t>
-  </si>
-  <si>
-    <t>e_w364421786*</t>
-  </si>
-  <si>
-    <t>p_w365883660</t>
-  </si>
-  <si>
-    <t>e_w365883660*</t>
-  </si>
-  <si>
-    <t>p_w366187313</t>
-  </si>
-  <si>
-    <t>e_w366187313*</t>
-  </si>
-  <si>
-    <t>p_w371593266</t>
-  </si>
-  <si>
-    <t>e_w371593266*</t>
-  </si>
-  <si>
-    <t>p_w1167367928</t>
-  </si>
-  <si>
-    <t>e_w1167367928*</t>
-  </si>
-  <si>
     <t>p_w377716686</t>
   </si>
   <si>
     <t>e_w377716686*</t>
   </si>
   <si>
-    <t>p_w379387167</t>
-  </si>
-  <si>
-    <t>e_w379387167*</t>
-  </si>
-  <si>
     <t>p_w380271836</t>
   </si>
   <si>
     <t>e_w380271836*</t>
   </si>
   <si>
-    <t>p_w380645355</t>
-  </si>
-  <si>
-    <t>e_w380645355*</t>
-  </si>
-  <si>
-    <t>p_w381266482</t>
-  </si>
-  <si>
-    <t>e_w381266482*</t>
-  </si>
-  <si>
-    <t>p_w381355305</t>
-  </si>
-  <si>
-    <t>e_w381355305*</t>
-  </si>
-  <si>
-    <t>p_w381517754</t>
-  </si>
-  <si>
-    <t>e_w381517754*</t>
-  </si>
-  <si>
-    <t>p_w382497416</t>
-  </si>
-  <si>
-    <t>e_w382497416*</t>
-  </si>
-  <si>
     <t>p_w383754584</t>
   </si>
   <si>
     <t>e_w383754584*</t>
   </si>
   <si>
-    <t>p_w383755661</t>
-  </si>
-  <si>
-    <t>e_w383755661*</t>
-  </si>
-  <si>
-    <t>p_w384575278</t>
-  </si>
-  <si>
-    <t>e_w384575278*</t>
+    <t>p_w569616471</t>
+  </si>
+  <si>
+    <t>e_w569616471*</t>
+  </si>
+  <si>
+    <t>p_w569616485</t>
+  </si>
+  <si>
+    <t>e_w569616485*</t>
+  </si>
+  <si>
+    <t>p_w574859222</t>
+  </si>
+  <si>
+    <t>e_w574859222*</t>
+  </si>
+  <si>
+    <t>p_w610844609</t>
+  </si>
+  <si>
+    <t>e_w610844609*</t>
+  </si>
+  <si>
+    <t>p_w635672953</t>
+  </si>
+  <si>
+    <t>e_w635672953*</t>
   </si>
   <si>
     <t>p_w694000747</t>
@@ -874,120 +472,6 @@
     <t>e_w694000747*</t>
   </si>
   <si>
-    <t>p_w385608518</t>
-  </si>
-  <si>
-    <t>e_w385608518*</t>
-  </si>
-  <si>
-    <t>p_w387693359</t>
-  </si>
-  <si>
-    <t>e_w387693359*</t>
-  </si>
-  <si>
-    <t>p_w387845900</t>
-  </si>
-  <si>
-    <t>e_w387845900*</t>
-  </si>
-  <si>
-    <t>p_w390634433</t>
-  </si>
-  <si>
-    <t>e_w390634433*</t>
-  </si>
-  <si>
-    <t>p_w464340115</t>
-  </si>
-  <si>
-    <t>e_w464340115*</t>
-  </si>
-  <si>
-    <t>p_w476360977</t>
-  </si>
-  <si>
-    <t>e_w476360977*</t>
-  </si>
-  <si>
-    <t>p_w533163474</t>
-  </si>
-  <si>
-    <t>e_w533163474*</t>
-  </si>
-  <si>
-    <t>p_w569616471</t>
-  </si>
-  <si>
-    <t>e_w569616471*</t>
-  </si>
-  <si>
-    <t>p_w569616485</t>
-  </si>
-  <si>
-    <t>e_w569616485*</t>
-  </si>
-  <si>
-    <t>p_w569616494</t>
-  </si>
-  <si>
-    <t>e_w569616494*</t>
-  </si>
-  <si>
-    <t>p_w574859222</t>
-  </si>
-  <si>
-    <t>e_w574859222*</t>
-  </si>
-  <si>
-    <t>p_w575738414</t>
-  </si>
-  <si>
-    <t>e_w575738414*</t>
-  </si>
-  <si>
-    <t>p_w589902332</t>
-  </si>
-  <si>
-    <t>e_w589902332*</t>
-  </si>
-  <si>
-    <t>p_w610844609</t>
-  </si>
-  <si>
-    <t>e_w610844609*</t>
-  </si>
-  <si>
-    <t>p_w611220827</t>
-  </si>
-  <si>
-    <t>e_w611220827*</t>
-  </si>
-  <si>
-    <t>p_w635672953</t>
-  </si>
-  <si>
-    <t>e_w635672953*</t>
-  </si>
-  <si>
-    <t>p_w637266751</t>
-  </si>
-  <si>
-    <t>e_w637266751*</t>
-  </si>
-  <si>
-    <t>p_w637288557</t>
-  </si>
-  <si>
-    <t>e_w637288557*</t>
-  </si>
-  <si>
-    <t>p_w694000748</t>
-  </si>
-  <si>
-    <t>e_w694000748*</t>
-  </si>
-  <si>
     <t>p_w694011250</t>
   </si>
   <si>
@@ -1000,24 +484,6 @@
     <t>e_w694011253*</t>
   </si>
   <si>
-    <t>p_w694205380</t>
-  </si>
-  <si>
-    <t>e_w694205380*</t>
-  </si>
-  <si>
-    <t>p_w694205382</t>
-  </si>
-  <si>
-    <t>e_w694205382*</t>
-  </si>
-  <si>
-    <t>p_w720223304</t>
-  </si>
-  <si>
-    <t>e_w720223304*</t>
-  </si>
-  <si>
     <t>p_w751040071</t>
   </si>
   <si>
@@ -1030,84 +496,12 @@
     <t>e_w833562295*</t>
   </si>
   <si>
-    <t>p_w936350097</t>
-  </si>
-  <si>
-    <t>e_w936350097*</t>
-  </si>
-  <si>
-    <t>p_w993660788</t>
-  </si>
-  <si>
-    <t>e_w993660788*</t>
-  </si>
-  <si>
-    <t>p_w1031001205</t>
-  </si>
-  <si>
-    <t>e_w1031001205*</t>
-  </si>
-  <si>
-    <t>p_w1031851533</t>
-  </si>
-  <si>
-    <t>e_w1031851533*</t>
-  </si>
-  <si>
-    <t>p_w1033225557</t>
-  </si>
-  <si>
-    <t>e_w1033225557*</t>
-  </si>
-  <si>
-    <t>p_w1033643187</t>
-  </si>
-  <si>
-    <t>e_w1033643187*</t>
-  </si>
-  <si>
-    <t>p_w1037301407</t>
-  </si>
-  <si>
-    <t>e_w1037301407*</t>
-  </si>
-  <si>
-    <t>p_w1056389360</t>
-  </si>
-  <si>
-    <t>e_w1056389360*</t>
-  </si>
-  <si>
-    <t>p_w1303896195</t>
-  </si>
-  <si>
-    <t>e_w1303896195*</t>
-  </si>
-  <si>
-    <t>p_w1354358035</t>
-  </si>
-  <si>
-    <t>e_w1354358035*</t>
-  </si>
-  <si>
     <t>p_w1377912118</t>
   </si>
   <si>
     <t>e_w1377912118*</t>
   </si>
   <si>
-    <t>p_DZ6</t>
-  </si>
-  <si>
-    <t>e_DZ6*</t>
-  </si>
-  <si>
-    <t>p_DZ24</t>
-  </si>
-  <si>
-    <t>e_DZ24*</t>
-  </si>
-  <si>
     <t>p_DZ45</t>
   </si>
   <si>
@@ -1120,172 +514,88 @@
     <t>e_DZ50*</t>
   </si>
   <si>
-    <t>p_DZ90</t>
-  </si>
-  <si>
-    <t>e_DZ90*</t>
-  </si>
-  <si>
-    <t>p_DZ47</t>
-  </si>
-  <si>
-    <t>e_DZ47*</t>
-  </si>
-  <si>
-    <t>p_DZ14</t>
-  </si>
-  <si>
-    <t>e_DZ14*</t>
-  </si>
-  <si>
     <t>p_DZ1</t>
   </si>
   <si>
     <t>e_DZ1*</t>
   </si>
   <si>
-    <t>p_DZ19</t>
-  </si>
-  <si>
-    <t>e_DZ19*</t>
-  </si>
-  <si>
-    <t>p_DZ123</t>
-  </si>
-  <si>
-    <t>e_DZ123*</t>
-  </si>
-  <si>
-    <t>p_DZ122</t>
-  </si>
-  <si>
-    <t>e_DZ122*</t>
-  </si>
-  <si>
-    <t>p_DZ154</t>
-  </si>
-  <si>
-    <t>e_DZ154*</t>
-  </si>
-  <si>
-    <t>p_DZ136</t>
-  </si>
-  <si>
-    <t>e_DZ136*</t>
-  </si>
-  <si>
-    <t>p_DZ141</t>
-  </si>
-  <si>
-    <t>e_DZ141*</t>
-  </si>
-  <si>
-    <t>p_DZ138</t>
-  </si>
-  <si>
-    <t>e_DZ138*</t>
-  </si>
-  <si>
-    <t>p_DZ5</t>
-  </si>
-  <si>
-    <t>e_DZ5*</t>
-  </si>
-  <si>
-    <t>p_DZ36</t>
-  </si>
-  <si>
-    <t>e_DZ36*</t>
-  </si>
-  <si>
-    <t>p_DZ30</t>
-  </si>
-  <si>
-    <t>e_DZ30*</t>
-  </si>
-  <si>
-    <t>p_DZ38</t>
-  </si>
-  <si>
-    <t>e_DZ38*</t>
-  </si>
-  <si>
-    <t>p_DZ114</t>
-  </si>
-  <si>
-    <t>e_DZ114*</t>
-  </si>
-  <si>
-    <t>p_DZ115</t>
-  </si>
-  <si>
-    <t>e_DZ115*</t>
-  </si>
-  <si>
-    <t>p_DZ8</t>
-  </si>
-  <si>
-    <t>e_DZ8*</t>
-  </si>
-  <si>
-    <t>p_DZ116</t>
-  </si>
-  <si>
-    <t>e_DZ116*</t>
-  </si>
-  <si>
-    <t>p_DZ112</t>
-  </si>
-  <si>
-    <t>e_DZ112*</t>
-  </si>
-  <si>
-    <t>p_DZ105</t>
-  </si>
-  <si>
-    <t>e_DZ105*</t>
-  </si>
-  <si>
-    <t>p_DZ101</t>
-  </si>
-  <si>
-    <t>e_DZ101*</t>
-  </si>
-  <si>
-    <t>p_DZ89</t>
-  </si>
-  <si>
-    <t>e_DZ89*</t>
-  </si>
-  <si>
-    <t>p_DZ93</t>
-  </si>
-  <si>
-    <t>e_DZ93*</t>
-  </si>
-  <si>
-    <t>p_DZ83</t>
-  </si>
-  <si>
-    <t>e_DZ83*</t>
-  </si>
-  <si>
-    <t>p_DZ85</t>
-  </si>
-  <si>
-    <t>e_DZ85*</t>
-  </si>
-  <si>
-    <t>p_DZ130</t>
-  </si>
-  <si>
-    <t>e_DZ130*</t>
-  </si>
-  <si>
-    <t>p_DZ118</t>
-  </si>
-  <si>
-    <t>e_DZ118*</t>
+    <t>p_DZ109</t>
+  </si>
+  <si>
+    <t>e_DZ109*</t>
+  </si>
+  <si>
+    <t>p_DZ72</t>
+  </si>
+  <si>
+    <t>e_DZ72*</t>
+  </si>
+  <si>
+    <t>p_DZ71</t>
+  </si>
+  <si>
+    <t>e_DZ71*</t>
+  </si>
+  <si>
+    <t>p_DZ2</t>
+  </si>
+  <si>
+    <t>e_DZ2*</t>
+  </si>
+  <si>
+    <t>p_DZ66</t>
+  </si>
+  <si>
+    <t>e_DZ66*</t>
+  </si>
+  <si>
+    <t>p_DZ65</t>
+  </si>
+  <si>
+    <t>e_DZ65*</t>
+  </si>
+  <si>
+    <t>p_DZ12</t>
+  </si>
+  <si>
+    <t>e_DZ12*</t>
+  </si>
+  <si>
+    <t>p_DZ13</t>
+  </si>
+  <si>
+    <t>e_DZ13*</t>
+  </si>
+  <si>
+    <t>p_DZ67</t>
+  </si>
+  <si>
+    <t>e_DZ67*</t>
+  </si>
+  <si>
+    <t>p_DZ108</t>
+  </si>
+  <si>
+    <t>e_DZ108*</t>
+  </si>
+  <si>
+    <t>p_DZ139</t>
+  </si>
+  <si>
+    <t>e_DZ139*</t>
+  </si>
+  <si>
+    <t>p_DZ134</t>
+  </si>
+  <si>
+    <t>e_DZ134*</t>
+  </si>
+  <si>
+    <t>p_DZ113</t>
+  </si>
+  <si>
+    <t>e_DZ113*</t>
   </si>
   <si>
     <t>p_DZ18</t>
@@ -1294,696 +604,18 @@
     <t>e_DZ18*</t>
   </si>
   <si>
-    <t>p_DZ11</t>
-  </si>
-  <si>
-    <t>e_DZ11*</t>
-  </si>
-  <si>
-    <t>p_DZ74</t>
-  </si>
-  <si>
-    <t>e_DZ74*</t>
-  </si>
-  <si>
-    <t>p_DZ69</t>
-  </si>
-  <si>
-    <t>e_DZ69*</t>
-  </si>
-  <si>
-    <t>p_DZ64</t>
-  </si>
-  <si>
-    <t>e_DZ64*</t>
-  </si>
-  <si>
-    <t>p_DZ79</t>
-  </si>
-  <si>
-    <t>e_DZ79*</t>
-  </si>
-  <si>
-    <t>p_DZ60</t>
-  </si>
-  <si>
-    <t>e_DZ60*</t>
-  </si>
-  <si>
-    <t>p_DZ44</t>
-  </si>
-  <si>
-    <t>e_DZ44*</t>
-  </si>
-  <si>
-    <t>p_DZ73</t>
-  </si>
-  <si>
-    <t>e_DZ73*</t>
-  </si>
-  <si>
-    <t>p_DZ72</t>
-  </si>
-  <si>
-    <t>e_DZ72*</t>
-  </si>
-  <si>
-    <t>p_DZ32</t>
-  </si>
-  <si>
-    <t>e_DZ32*</t>
-  </si>
-  <si>
-    <t>p_DZ31</t>
-  </si>
-  <si>
-    <t>e_DZ31*</t>
-  </si>
-  <si>
-    <t>p_DZ91</t>
-  </si>
-  <si>
-    <t>e_DZ91*</t>
-  </si>
-  <si>
-    <t>p_DZ104</t>
-  </si>
-  <si>
-    <t>e_DZ104*</t>
-  </si>
-  <si>
-    <t>p_DZ103</t>
-  </si>
-  <si>
-    <t>e_DZ103*</t>
-  </si>
-  <si>
-    <t>p_DZ21</t>
-  </si>
-  <si>
-    <t>e_DZ21*</t>
-  </si>
-  <si>
-    <t>p_DZ49</t>
-  </si>
-  <si>
-    <t>e_DZ49*</t>
-  </si>
-  <si>
-    <t>p_DZ20</t>
-  </si>
-  <si>
-    <t>e_DZ20*</t>
-  </si>
-  <si>
-    <t>p_DZ155</t>
-  </si>
-  <si>
-    <t>e_DZ155*</t>
-  </si>
-  <si>
-    <t>p_DZ140</t>
-  </si>
-  <si>
-    <t>e_DZ140*</t>
-  </si>
-  <si>
-    <t>p_DZ40</t>
-  </si>
-  <si>
-    <t>e_DZ40*</t>
-  </si>
-  <si>
-    <t>p_DZ23</t>
-  </si>
-  <si>
-    <t>e_DZ23*</t>
-  </si>
-  <si>
-    <t>p_DZ56</t>
-  </si>
-  <si>
-    <t>e_DZ56*</t>
-  </si>
-  <si>
-    <t>p_DZ109</t>
-  </si>
-  <si>
-    <t>e_DZ109*</t>
-  </si>
-  <si>
-    <t>p_DZ16</t>
-  </si>
-  <si>
-    <t>e_DZ16*</t>
-  </si>
-  <si>
-    <t>p_DZ70</t>
-  </si>
-  <si>
-    <t>e_DZ70*</t>
-  </si>
-  <si>
-    <t>p_DZ71</t>
-  </si>
-  <si>
-    <t>e_DZ71*</t>
-  </si>
-  <si>
-    <t>p_DZ133</t>
-  </si>
-  <si>
-    <t>e_DZ133*</t>
-  </si>
-  <si>
-    <t>p_DZ2</t>
-  </si>
-  <si>
-    <t>e_DZ2*</t>
-  </si>
-  <si>
-    <t>p_DZ53</t>
-  </si>
-  <si>
-    <t>e_DZ53*</t>
-  </si>
-  <si>
-    <t>p_DZ55</t>
-  </si>
-  <si>
-    <t>e_DZ55*</t>
-  </si>
-  <si>
-    <t>p_DZ126</t>
-  </si>
-  <si>
-    <t>e_DZ126*</t>
-  </si>
-  <si>
-    <t>p_DZ66</t>
-  </si>
-  <si>
-    <t>e_DZ66*</t>
-  </si>
-  <si>
-    <t>p_DZ35</t>
-  </si>
-  <si>
-    <t>e_DZ35*</t>
-  </si>
-  <si>
-    <t>p_DZ65</t>
-  </si>
-  <si>
-    <t>e_DZ65*</t>
-  </si>
-  <si>
-    <t>p_DZ117</t>
-  </si>
-  <si>
-    <t>e_DZ117*</t>
-  </si>
-  <si>
-    <t>p_DZ124</t>
-  </si>
-  <si>
-    <t>e_DZ124*</t>
-  </si>
-  <si>
-    <t>p_DZ110</t>
-  </si>
-  <si>
-    <t>e_DZ110*</t>
-  </si>
-  <si>
-    <t>p_DZ102</t>
-  </si>
-  <si>
-    <t>e_DZ102*</t>
-  </si>
-  <si>
-    <t>p_DZ97</t>
-  </si>
-  <si>
-    <t>e_DZ97*</t>
-  </si>
-  <si>
-    <t>p_DZ142</t>
-  </si>
-  <si>
-    <t>e_DZ142*</t>
-  </si>
-  <si>
-    <t>p_DZ75</t>
-  </si>
-  <si>
-    <t>e_DZ75*</t>
-  </si>
-  <si>
-    <t>p_DZ12</t>
-  </si>
-  <si>
-    <t>e_DZ12*</t>
-  </si>
-  <si>
-    <t>p_DZ150</t>
-  </si>
-  <si>
-    <t>e_DZ150*</t>
-  </si>
-  <si>
-    <t>p_DZ151</t>
-  </si>
-  <si>
-    <t>e_DZ151*</t>
-  </si>
-  <si>
-    <t>p_DZ152</t>
-  </si>
-  <si>
-    <t>e_DZ152*</t>
-  </si>
-  <si>
-    <t>p_DZ13</t>
-  </si>
-  <si>
-    <t>e_DZ13*</t>
-  </si>
-  <si>
-    <t>p_DZ7</t>
-  </si>
-  <si>
-    <t>e_DZ7*</t>
-  </si>
-  <si>
-    <t>p_DZ4</t>
-  </si>
-  <si>
-    <t>e_DZ4*</t>
-  </si>
-  <si>
-    <t>p_DZ43</t>
-  </si>
-  <si>
-    <t>e_DZ43*</t>
-  </si>
-  <si>
-    <t>p_DZ77</t>
-  </si>
-  <si>
-    <t>e_DZ77*</t>
-  </si>
-  <si>
-    <t>p_DZ157</t>
-  </si>
-  <si>
-    <t>e_DZ157*</t>
-  </si>
-  <si>
-    <t>p_DZ158</t>
-  </si>
-  <si>
-    <t>e_DZ158*</t>
-  </si>
-  <si>
-    <t>p_DZ27</t>
-  </si>
-  <si>
-    <t>e_DZ27*</t>
-  </si>
-  <si>
-    <t>p_DZ29</t>
-  </si>
-  <si>
-    <t>e_DZ29*</t>
-  </si>
-  <si>
-    <t>p_DZ67</t>
-  </si>
-  <si>
-    <t>e_DZ67*</t>
-  </si>
-  <si>
-    <t>p_DZ160</t>
-  </si>
-  <si>
-    <t>e_DZ160*</t>
-  </si>
-  <si>
-    <t>p_DZ108</t>
-  </si>
-  <si>
-    <t>e_DZ108*</t>
-  </si>
-  <si>
-    <t>p_DZ146</t>
-  </si>
-  <si>
-    <t>e_DZ146*</t>
-  </si>
-  <si>
-    <t>p_DZ147</t>
-  </si>
-  <si>
-    <t>e_DZ147*</t>
-  </si>
-  <si>
-    <t>p_DZ148</t>
-  </si>
-  <si>
-    <t>e_DZ148*</t>
-  </si>
-  <si>
-    <t>p_DZ139</t>
-  </si>
-  <si>
-    <t>e_DZ139*</t>
-  </si>
-  <si>
-    <t>p_DZ58</t>
-  </si>
-  <si>
-    <t>e_DZ58*</t>
-  </si>
-  <si>
-    <t>p_DZ127</t>
-  </si>
-  <si>
-    <t>e_DZ127*</t>
-  </si>
-  <si>
-    <t>p_DZ134</t>
-  </si>
-  <si>
-    <t>e_DZ134*</t>
-  </si>
-  <si>
-    <t>p_DZ113</t>
-  </si>
-  <si>
-    <t>e_DZ113*</t>
-  </si>
-  <si>
-    <t>p_DZ132</t>
-  </si>
-  <si>
-    <t>e_DZ132*</t>
-  </si>
-  <si>
-    <t>p_DZ10</t>
-  </si>
-  <si>
-    <t>e_DZ10*</t>
-  </si>
-  <si>
-    <t>p_DZ80</t>
-  </si>
-  <si>
-    <t>e_DZ80*</t>
-  </si>
-  <si>
-    <t>p_DZ39</t>
-  </si>
-  <si>
-    <t>e_DZ39*</t>
-  </si>
-  <si>
-    <t>p_DZ120</t>
-  </si>
-  <si>
-    <t>e_DZ120*</t>
-  </si>
-  <si>
-    <t>p_DZ153</t>
-  </si>
-  <si>
-    <t>e_DZ153*</t>
-  </si>
-  <si>
-    <t>p_DZ121</t>
-  </si>
-  <si>
-    <t>e_DZ121*</t>
-  </si>
-  <si>
-    <t>p_DZ137</t>
-  </si>
-  <si>
-    <t>e_DZ137*</t>
-  </si>
-  <si>
-    <t>p_DZ48</t>
-  </si>
-  <si>
-    <t>e_DZ48*</t>
-  </si>
-  <si>
-    <t>p_DZ34</t>
-  </si>
-  <si>
-    <t>e_DZ34*</t>
-  </si>
-  <si>
-    <t>p_DZ26</t>
-  </si>
-  <si>
-    <t>e_DZ26*</t>
-  </si>
-  <si>
-    <t>p_DZ15</t>
-  </si>
-  <si>
-    <t>e_DZ15*</t>
-  </si>
-  <si>
-    <t>p_DZ119</t>
-  </si>
-  <si>
-    <t>e_DZ119*</t>
-  </si>
-  <si>
-    <t>p_DZ92</t>
-  </si>
-  <si>
-    <t>e_DZ92*</t>
-  </si>
-  <si>
-    <t>p_DZ88</t>
-  </si>
-  <si>
-    <t>e_DZ88*</t>
-  </si>
-  <si>
-    <t>p_DZ81</t>
-  </si>
-  <si>
-    <t>e_DZ81*</t>
-  </si>
-  <si>
-    <t>p_DZ95</t>
-  </si>
-  <si>
-    <t>e_DZ95*</t>
-  </si>
-  <si>
-    <t>p_DZ78</t>
-  </si>
-  <si>
-    <t>e_DZ78*</t>
-  </si>
-  <si>
-    <t>p_DZ42</t>
-  </si>
-  <si>
-    <t>e_DZ42*</t>
-  </si>
-  <si>
-    <t>p_DZ62</t>
-  </si>
-  <si>
-    <t>e_DZ62*</t>
-  </si>
-  <si>
-    <t>p_DZ61</t>
-  </si>
-  <si>
-    <t>e_DZ61*</t>
-  </si>
-  <si>
-    <t>p_DZ59</t>
-  </si>
-  <si>
-    <t>e_DZ59*</t>
-  </si>
-  <si>
-    <t>p_DZ33</t>
-  </si>
-  <si>
-    <t>e_DZ33*</t>
-  </si>
-  <si>
-    <t>p_DZ54</t>
-  </si>
-  <si>
-    <t>e_DZ54*</t>
-  </si>
-  <si>
-    <t>p_DZ111</t>
-  </si>
-  <si>
-    <t>e_DZ111*</t>
-  </si>
-  <si>
-    <t>p_DZ145</t>
-  </si>
-  <si>
-    <t>e_DZ145*</t>
-  </si>
-  <si>
-    <t>p_DZ9</t>
-  </si>
-  <si>
-    <t>e_DZ9*</t>
-  </si>
-  <si>
-    <t>p_DZ17</t>
-  </si>
-  <si>
-    <t>e_DZ17*</t>
-  </si>
-  <si>
-    <t>p_DZ22</t>
-  </si>
-  <si>
-    <t>e_DZ22*</t>
-  </si>
-  <si>
-    <t>p_DZ46</t>
-  </si>
-  <si>
-    <t>e_DZ46*</t>
-  </si>
-  <si>
-    <t>p_DZ57</t>
-  </si>
-  <si>
-    <t>e_DZ57*</t>
-  </si>
-  <si>
-    <t>p_DZ86</t>
-  </si>
-  <si>
-    <t>e_DZ86*</t>
-  </si>
-  <si>
-    <t>p_DZ37</t>
-  </si>
-  <si>
-    <t>e_DZ37*</t>
-  </si>
-  <si>
-    <t>p_DZ129</t>
-  </si>
-  <si>
-    <t>e_DZ129*</t>
-  </si>
-  <si>
-    <t>p_DZ52</t>
-  </si>
-  <si>
-    <t>e_DZ52*</t>
-  </si>
-  <si>
-    <t>p_DZ107</t>
-  </si>
-  <si>
-    <t>e_DZ107*</t>
-  </si>
-  <si>
     <t>p_DZ99</t>
   </si>
   <si>
     <t>e_DZ99*</t>
   </si>
   <si>
-    <t>p_DZ100</t>
-  </si>
-  <si>
-    <t>e_DZ100*</t>
-  </si>
-  <si>
-    <t>p_DZ143</t>
-  </si>
-  <si>
-    <t>e_DZ143*</t>
-  </si>
-  <si>
-    <t>p_DZ51</t>
-  </si>
-  <si>
-    <t>e_DZ51*</t>
-  </si>
-  <si>
-    <t>p_DZ94</t>
-  </si>
-  <si>
-    <t>e_DZ94*</t>
-  </si>
-  <si>
-    <t>p_DZ98</t>
-  </si>
-  <si>
-    <t>e_DZ98*</t>
-  </si>
-  <si>
     <t>p_DZ96</t>
   </si>
   <si>
     <t>e_DZ96*</t>
   </si>
   <si>
-    <t>p_DZ149</t>
-  </si>
-  <si>
-    <t>e_DZ149*</t>
-  </si>
-  <si>
-    <t>p_DZ3</t>
-  </si>
-  <si>
-    <t>e_DZ3*</t>
-  </si>
-  <si>
-    <t>p_DZ76</t>
-  </si>
-  <si>
-    <t>e_DZ76*</t>
-  </si>
-  <si>
-    <t>p_DZ156</t>
-  </si>
-  <si>
-    <t>e_DZ156*</t>
-  </si>
-  <si>
-    <t>p_DZ159</t>
-  </si>
-  <si>
-    <t>e_DZ159*</t>
-  </si>
-  <si>
-    <t>p_DZ28</t>
-  </si>
-  <si>
-    <t>e_DZ28*</t>
-  </si>
-  <si>
-    <t>p_DZ25</t>
-  </si>
-  <si>
-    <t>e_DZ25*</t>
-  </si>
-  <si>
     <t>p_DZ63</t>
   </si>
   <si>
@@ -2002,46 +634,10 @@
     <t>e_DZ128*</t>
   </si>
   <si>
-    <t>p_DZ144</t>
-  </si>
-  <si>
-    <t>e_DZ144*</t>
-  </si>
-  <si>
     <t>p_DZ135</t>
   </si>
   <si>
     <t>e_DZ135*</t>
-  </si>
-  <si>
-    <t>p_DZ84</t>
-  </si>
-  <si>
-    <t>e_DZ84*</t>
-  </si>
-  <si>
-    <t>p_DZ82</t>
-  </si>
-  <si>
-    <t>e_DZ82*</t>
-  </si>
-  <si>
-    <t>p_DZ131</t>
-  </si>
-  <si>
-    <t>e_DZ131*</t>
-  </si>
-  <si>
-    <t>p_DZ125</t>
-  </si>
-  <si>
-    <t>e_DZ125*</t>
-  </si>
-  <si>
-    <t>p_DZ106</t>
-  </si>
-  <si>
-    <t>e_DZ106*</t>
   </si>
   <si>
     <t>rez_spv_001</t>
@@ -3719,8 +2315,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFA9854-6934-4FBD-8983-99D635CE5E0F}">
-  <dimension ref="B9:E432"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013E078F-6DD0-42C2-86A0-920142156F6A}">
+  <dimension ref="B9:E198"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -6371,3282 +4967,6 @@
         <v>479</v>
       </c>
       <c r="E198" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B199" t="s">
-        <v>480</v>
-      </c>
-      <c r="C199" t="s">
-        <v>481</v>
-      </c>
-      <c r="D199" t="s">
-        <v>481</v>
-      </c>
-      <c r="E199" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B200" t="s">
-        <v>482</v>
-      </c>
-      <c r="C200" t="s">
-        <v>483</v>
-      </c>
-      <c r="D200" t="s">
-        <v>483</v>
-      </c>
-      <c r="E200" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B201" t="s">
-        <v>484</v>
-      </c>
-      <c r="C201" t="s">
-        <v>485</v>
-      </c>
-      <c r="D201" t="s">
-        <v>485</v>
-      </c>
-      <c r="E201" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B202" t="s">
-        <v>486</v>
-      </c>
-      <c r="C202" t="s">
-        <v>487</v>
-      </c>
-      <c r="D202" t="s">
-        <v>487</v>
-      </c>
-      <c r="E202" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B203" t="s">
-        <v>488</v>
-      </c>
-      <c r="C203" t="s">
-        <v>489</v>
-      </c>
-      <c r="D203" t="s">
-        <v>489</v>
-      </c>
-      <c r="E203" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B204" t="s">
-        <v>490</v>
-      </c>
-      <c r="C204" t="s">
-        <v>491</v>
-      </c>
-      <c r="D204" t="s">
-        <v>491</v>
-      </c>
-      <c r="E204" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B205" t="s">
-        <v>492</v>
-      </c>
-      <c r="C205" t="s">
-        <v>493</v>
-      </c>
-      <c r="D205" t="s">
-        <v>493</v>
-      </c>
-      <c r="E205" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B206" t="s">
-        <v>494</v>
-      </c>
-      <c r="C206" t="s">
-        <v>495</v>
-      </c>
-      <c r="D206" t="s">
-        <v>495</v>
-      </c>
-      <c r="E206" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B207" t="s">
-        <v>496</v>
-      </c>
-      <c r="C207" t="s">
-        <v>497</v>
-      </c>
-      <c r="D207" t="s">
-        <v>497</v>
-      </c>
-      <c r="E207" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B208" t="s">
-        <v>498</v>
-      </c>
-      <c r="C208" t="s">
-        <v>499</v>
-      </c>
-      <c r="D208" t="s">
-        <v>499</v>
-      </c>
-      <c r="E208" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B209" t="s">
-        <v>500</v>
-      </c>
-      <c r="C209" t="s">
-        <v>501</v>
-      </c>
-      <c r="D209" t="s">
-        <v>501</v>
-      </c>
-      <c r="E209" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B210" t="s">
-        <v>502</v>
-      </c>
-      <c r="C210" t="s">
-        <v>503</v>
-      </c>
-      <c r="D210" t="s">
-        <v>503</v>
-      </c>
-      <c r="E210" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B211" t="s">
-        <v>504</v>
-      </c>
-      <c r="C211" t="s">
-        <v>505</v>
-      </c>
-      <c r="D211" t="s">
-        <v>505</v>
-      </c>
-      <c r="E211" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B212" t="s">
-        <v>506</v>
-      </c>
-      <c r="C212" t="s">
-        <v>507</v>
-      </c>
-      <c r="D212" t="s">
-        <v>507</v>
-      </c>
-      <c r="E212" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B213" t="s">
-        <v>508</v>
-      </c>
-      <c r="C213" t="s">
-        <v>509</v>
-      </c>
-      <c r="D213" t="s">
-        <v>509</v>
-      </c>
-      <c r="E213" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B214" t="s">
-        <v>510</v>
-      </c>
-      <c r="C214" t="s">
-        <v>511</v>
-      </c>
-      <c r="D214" t="s">
-        <v>511</v>
-      </c>
-      <c r="E214" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B215" t="s">
-        <v>512</v>
-      </c>
-      <c r="C215" t="s">
-        <v>513</v>
-      </c>
-      <c r="D215" t="s">
-        <v>513</v>
-      </c>
-      <c r="E215" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B216" t="s">
-        <v>514</v>
-      </c>
-      <c r="C216" t="s">
-        <v>515</v>
-      </c>
-      <c r="D216" t="s">
-        <v>515</v>
-      </c>
-      <c r="E216" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B217" t="s">
-        <v>516</v>
-      </c>
-      <c r="C217" t="s">
-        <v>517</v>
-      </c>
-      <c r="D217" t="s">
-        <v>517</v>
-      </c>
-      <c r="E217" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B218" t="s">
-        <v>518</v>
-      </c>
-      <c r="C218" t="s">
-        <v>519</v>
-      </c>
-      <c r="D218" t="s">
-        <v>519</v>
-      </c>
-      <c r="E218" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B219" t="s">
-        <v>520</v>
-      </c>
-      <c r="C219" t="s">
-        <v>521</v>
-      </c>
-      <c r="D219" t="s">
-        <v>521</v>
-      </c>
-      <c r="E219" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B220" t="s">
-        <v>522</v>
-      </c>
-      <c r="C220" t="s">
-        <v>523</v>
-      </c>
-      <c r="D220" t="s">
-        <v>523</v>
-      </c>
-      <c r="E220" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B221" t="s">
-        <v>524</v>
-      </c>
-      <c r="C221" t="s">
-        <v>525</v>
-      </c>
-      <c r="D221" t="s">
-        <v>525</v>
-      </c>
-      <c r="E221" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B222" t="s">
-        <v>526</v>
-      </c>
-      <c r="C222" t="s">
-        <v>527</v>
-      </c>
-      <c r="D222" t="s">
-        <v>527</v>
-      </c>
-      <c r="E222" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B223" t="s">
-        <v>528</v>
-      </c>
-      <c r="C223" t="s">
-        <v>529</v>
-      </c>
-      <c r="D223" t="s">
-        <v>529</v>
-      </c>
-      <c r="E223" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B224" t="s">
-        <v>530</v>
-      </c>
-      <c r="C224" t="s">
-        <v>531</v>
-      </c>
-      <c r="D224" t="s">
-        <v>531</v>
-      </c>
-      <c r="E224" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B225" t="s">
-        <v>532</v>
-      </c>
-      <c r="C225" t="s">
-        <v>533</v>
-      </c>
-      <c r="D225" t="s">
-        <v>533</v>
-      </c>
-      <c r="E225" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B226" t="s">
-        <v>534</v>
-      </c>
-      <c r="C226" t="s">
-        <v>535</v>
-      </c>
-      <c r="D226" t="s">
-        <v>535</v>
-      </c>
-      <c r="E226" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B227" t="s">
-        <v>536</v>
-      </c>
-      <c r="C227" t="s">
-        <v>537</v>
-      </c>
-      <c r="D227" t="s">
-        <v>537</v>
-      </c>
-      <c r="E227" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B228" t="s">
-        <v>538</v>
-      </c>
-      <c r="C228" t="s">
-        <v>539</v>
-      </c>
-      <c r="D228" t="s">
-        <v>539</v>
-      </c>
-      <c r="E228" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B229" t="s">
-        <v>540</v>
-      </c>
-      <c r="C229" t="s">
-        <v>541</v>
-      </c>
-      <c r="D229" t="s">
-        <v>541</v>
-      </c>
-      <c r="E229" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B230" t="s">
-        <v>542</v>
-      </c>
-      <c r="C230" t="s">
-        <v>543</v>
-      </c>
-      <c r="D230" t="s">
-        <v>543</v>
-      </c>
-      <c r="E230" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B231" t="s">
-        <v>544</v>
-      </c>
-      <c r="C231" t="s">
-        <v>545</v>
-      </c>
-      <c r="D231" t="s">
-        <v>545</v>
-      </c>
-      <c r="E231" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B232" t="s">
-        <v>546</v>
-      </c>
-      <c r="C232" t="s">
-        <v>547</v>
-      </c>
-      <c r="D232" t="s">
-        <v>547</v>
-      </c>
-      <c r="E232" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B233" t="s">
-        <v>548</v>
-      </c>
-      <c r="C233" t="s">
-        <v>549</v>
-      </c>
-      <c r="D233" t="s">
-        <v>549</v>
-      </c>
-      <c r="E233" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B234" t="s">
-        <v>550</v>
-      </c>
-      <c r="C234" t="s">
-        <v>551</v>
-      </c>
-      <c r="D234" t="s">
-        <v>551</v>
-      </c>
-      <c r="E234" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B235" t="s">
-        <v>552</v>
-      </c>
-      <c r="C235" t="s">
-        <v>553</v>
-      </c>
-      <c r="D235" t="s">
-        <v>553</v>
-      </c>
-      <c r="E235" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B236" t="s">
-        <v>554</v>
-      </c>
-      <c r="C236" t="s">
-        <v>555</v>
-      </c>
-      <c r="D236" t="s">
-        <v>555</v>
-      </c>
-      <c r="E236" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B237" t="s">
-        <v>556</v>
-      </c>
-      <c r="C237" t="s">
-        <v>557</v>
-      </c>
-      <c r="D237" t="s">
-        <v>557</v>
-      </c>
-      <c r="E237" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B238" t="s">
-        <v>558</v>
-      </c>
-      <c r="C238" t="s">
-        <v>559</v>
-      </c>
-      <c r="D238" t="s">
-        <v>559</v>
-      </c>
-      <c r="E238" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B239" t="s">
-        <v>560</v>
-      </c>
-      <c r="C239" t="s">
-        <v>561</v>
-      </c>
-      <c r="D239" t="s">
-        <v>561</v>
-      </c>
-      <c r="E239" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B240" t="s">
-        <v>562</v>
-      </c>
-      <c r="C240" t="s">
-        <v>563</v>
-      </c>
-      <c r="D240" t="s">
-        <v>563</v>
-      </c>
-      <c r="E240" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B241" t="s">
-        <v>564</v>
-      </c>
-      <c r="C241" t="s">
-        <v>565</v>
-      </c>
-      <c r="D241" t="s">
-        <v>565</v>
-      </c>
-      <c r="E241" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B242" t="s">
-        <v>566</v>
-      </c>
-      <c r="C242" t="s">
-        <v>567</v>
-      </c>
-      <c r="D242" t="s">
-        <v>567</v>
-      </c>
-      <c r="E242" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B243" t="s">
-        <v>568</v>
-      </c>
-      <c r="C243" t="s">
-        <v>569</v>
-      </c>
-      <c r="D243" t="s">
-        <v>569</v>
-      </c>
-      <c r="E243" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B244" t="s">
-        <v>570</v>
-      </c>
-      <c r="C244" t="s">
-        <v>571</v>
-      </c>
-      <c r="D244" t="s">
-        <v>571</v>
-      </c>
-      <c r="E244" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B245" t="s">
-        <v>572</v>
-      </c>
-      <c r="C245" t="s">
-        <v>573</v>
-      </c>
-      <c r="D245" t="s">
-        <v>573</v>
-      </c>
-      <c r="E245" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B246" t="s">
-        <v>574</v>
-      </c>
-      <c r="C246" t="s">
-        <v>575</v>
-      </c>
-      <c r="D246" t="s">
-        <v>575</v>
-      </c>
-      <c r="E246" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B247" t="s">
-        <v>576</v>
-      </c>
-      <c r="C247" t="s">
-        <v>577</v>
-      </c>
-      <c r="D247" t="s">
-        <v>577</v>
-      </c>
-      <c r="E247" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B248" t="s">
-        <v>578</v>
-      </c>
-      <c r="C248" t="s">
-        <v>579</v>
-      </c>
-      <c r="D248" t="s">
-        <v>579</v>
-      </c>
-      <c r="E248" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B249" t="s">
-        <v>580</v>
-      </c>
-      <c r="C249" t="s">
-        <v>581</v>
-      </c>
-      <c r="D249" t="s">
-        <v>581</v>
-      </c>
-      <c r="E249" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B250" t="s">
-        <v>582</v>
-      </c>
-      <c r="C250" t="s">
-        <v>583</v>
-      </c>
-      <c r="D250" t="s">
-        <v>583</v>
-      </c>
-      <c r="E250" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B251" t="s">
-        <v>584</v>
-      </c>
-      <c r="C251" t="s">
-        <v>585</v>
-      </c>
-      <c r="D251" t="s">
-        <v>585</v>
-      </c>
-      <c r="E251" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B252" t="s">
-        <v>586</v>
-      </c>
-      <c r="C252" t="s">
-        <v>587</v>
-      </c>
-      <c r="D252" t="s">
-        <v>587</v>
-      </c>
-      <c r="E252" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B253" t="s">
-        <v>588</v>
-      </c>
-      <c r="C253" t="s">
-        <v>589</v>
-      </c>
-      <c r="D253" t="s">
-        <v>589</v>
-      </c>
-      <c r="E253" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B254" t="s">
-        <v>590</v>
-      </c>
-      <c r="C254" t="s">
-        <v>591</v>
-      </c>
-      <c r="D254" t="s">
-        <v>591</v>
-      </c>
-      <c r="E254" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B255" t="s">
-        <v>592</v>
-      </c>
-      <c r="C255" t="s">
-        <v>593</v>
-      </c>
-      <c r="D255" t="s">
-        <v>593</v>
-      </c>
-      <c r="E255" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B256" t="s">
-        <v>594</v>
-      </c>
-      <c r="C256" t="s">
-        <v>595</v>
-      </c>
-      <c r="D256" t="s">
-        <v>595</v>
-      </c>
-      <c r="E256" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B257" t="s">
-        <v>596</v>
-      </c>
-      <c r="C257" t="s">
-        <v>597</v>
-      </c>
-      <c r="D257" t="s">
-        <v>597</v>
-      </c>
-      <c r="E257" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B258" t="s">
-        <v>598</v>
-      </c>
-      <c r="C258" t="s">
-        <v>599</v>
-      </c>
-      <c r="D258" t="s">
-        <v>599</v>
-      </c>
-      <c r="E258" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B259" t="s">
-        <v>600</v>
-      </c>
-      <c r="C259" t="s">
-        <v>601</v>
-      </c>
-      <c r="D259" t="s">
-        <v>601</v>
-      </c>
-      <c r="E259" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B260" t="s">
-        <v>602</v>
-      </c>
-      <c r="C260" t="s">
-        <v>603</v>
-      </c>
-      <c r="D260" t="s">
-        <v>603</v>
-      </c>
-      <c r="E260" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B261" t="s">
-        <v>604</v>
-      </c>
-      <c r="C261" t="s">
-        <v>605</v>
-      </c>
-      <c r="D261" t="s">
-        <v>605</v>
-      </c>
-      <c r="E261" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B262" t="s">
-        <v>606</v>
-      </c>
-      <c r="C262" t="s">
-        <v>607</v>
-      </c>
-      <c r="D262" t="s">
-        <v>607</v>
-      </c>
-      <c r="E262" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B263" t="s">
-        <v>608</v>
-      </c>
-      <c r="C263" t="s">
-        <v>609</v>
-      </c>
-      <c r="D263" t="s">
-        <v>609</v>
-      </c>
-      <c r="E263" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B264" t="s">
-        <v>610</v>
-      </c>
-      <c r="C264" t="s">
-        <v>611</v>
-      </c>
-      <c r="D264" t="s">
-        <v>611</v>
-      </c>
-      <c r="E264" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B265" t="s">
-        <v>612</v>
-      </c>
-      <c r="C265" t="s">
-        <v>613</v>
-      </c>
-      <c r="D265" t="s">
-        <v>613</v>
-      </c>
-      <c r="E265" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B266" t="s">
-        <v>614</v>
-      </c>
-      <c r="C266" t="s">
-        <v>615</v>
-      </c>
-      <c r="D266" t="s">
-        <v>615</v>
-      </c>
-      <c r="E266" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B267" t="s">
-        <v>616</v>
-      </c>
-      <c r="C267" t="s">
-        <v>617</v>
-      </c>
-      <c r="D267" t="s">
-        <v>617</v>
-      </c>
-      <c r="E267" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B268" t="s">
-        <v>618</v>
-      </c>
-      <c r="C268" t="s">
-        <v>619</v>
-      </c>
-      <c r="D268" t="s">
-        <v>619</v>
-      </c>
-      <c r="E268" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B269" t="s">
-        <v>620</v>
-      </c>
-      <c r="C269" t="s">
-        <v>621</v>
-      </c>
-      <c r="D269" t="s">
-        <v>621</v>
-      </c>
-      <c r="E269" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B270" t="s">
-        <v>622</v>
-      </c>
-      <c r="C270" t="s">
-        <v>623</v>
-      </c>
-      <c r="D270" t="s">
-        <v>623</v>
-      </c>
-      <c r="E270" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B271" t="s">
-        <v>624</v>
-      </c>
-      <c r="C271" t="s">
-        <v>625</v>
-      </c>
-      <c r="D271" t="s">
-        <v>625</v>
-      </c>
-      <c r="E271" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B272" t="s">
-        <v>626</v>
-      </c>
-      <c r="C272" t="s">
-        <v>627</v>
-      </c>
-      <c r="D272" t="s">
-        <v>627</v>
-      </c>
-      <c r="E272" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B273" t="s">
-        <v>628</v>
-      </c>
-      <c r="C273" t="s">
-        <v>629</v>
-      </c>
-      <c r="D273" t="s">
-        <v>629</v>
-      </c>
-      <c r="E273" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B274" t="s">
-        <v>630</v>
-      </c>
-      <c r="C274" t="s">
-        <v>631</v>
-      </c>
-      <c r="D274" t="s">
-        <v>631</v>
-      </c>
-      <c r="E274" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B275" t="s">
-        <v>632</v>
-      </c>
-      <c r="C275" t="s">
-        <v>633</v>
-      </c>
-      <c r="D275" t="s">
-        <v>633</v>
-      </c>
-      <c r="E275" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B276" t="s">
-        <v>634</v>
-      </c>
-      <c r="C276" t="s">
-        <v>635</v>
-      </c>
-      <c r="D276" t="s">
-        <v>635</v>
-      </c>
-      <c r="E276" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B277" t="s">
-        <v>636</v>
-      </c>
-      <c r="C277" t="s">
-        <v>637</v>
-      </c>
-      <c r="D277" t="s">
-        <v>637</v>
-      </c>
-      <c r="E277" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B278" t="s">
-        <v>638</v>
-      </c>
-      <c r="C278" t="s">
-        <v>639</v>
-      </c>
-      <c r="D278" t="s">
-        <v>639</v>
-      </c>
-      <c r="E278" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B279" t="s">
-        <v>640</v>
-      </c>
-      <c r="C279" t="s">
-        <v>641</v>
-      </c>
-      <c r="D279" t="s">
-        <v>641</v>
-      </c>
-      <c r="E279" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B280" t="s">
-        <v>642</v>
-      </c>
-      <c r="C280" t="s">
-        <v>643</v>
-      </c>
-      <c r="D280" t="s">
-        <v>643</v>
-      </c>
-      <c r="E280" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B281" t="s">
-        <v>644</v>
-      </c>
-      <c r="C281" t="s">
-        <v>645</v>
-      </c>
-      <c r="D281" t="s">
-        <v>645</v>
-      </c>
-      <c r="E281" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B282" t="s">
-        <v>646</v>
-      </c>
-      <c r="C282" t="s">
-        <v>647</v>
-      </c>
-      <c r="D282" t="s">
-        <v>647</v>
-      </c>
-      <c r="E282" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B283" t="s">
-        <v>648</v>
-      </c>
-      <c r="C283" t="s">
-        <v>649</v>
-      </c>
-      <c r="D283" t="s">
-        <v>649</v>
-      </c>
-      <c r="E283" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B284" t="s">
-        <v>650</v>
-      </c>
-      <c r="C284" t="s">
-        <v>651</v>
-      </c>
-      <c r="D284" t="s">
-        <v>651</v>
-      </c>
-      <c r="E284" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B285" t="s">
-        <v>652</v>
-      </c>
-      <c r="C285" t="s">
-        <v>653</v>
-      </c>
-      <c r="D285" t="s">
-        <v>653</v>
-      </c>
-      <c r="E285" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B286" t="s">
-        <v>654</v>
-      </c>
-      <c r="C286" t="s">
-        <v>655</v>
-      </c>
-      <c r="D286" t="s">
-        <v>655</v>
-      </c>
-      <c r="E286" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B287" t="s">
-        <v>656</v>
-      </c>
-      <c r="C287" t="s">
-        <v>657</v>
-      </c>
-      <c r="D287" t="s">
-        <v>657</v>
-      </c>
-      <c r="E287" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B288" t="s">
-        <v>658</v>
-      </c>
-      <c r="C288" t="s">
-        <v>659</v>
-      </c>
-      <c r="D288" t="s">
-        <v>659</v>
-      </c>
-      <c r="E288" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B289" t="s">
-        <v>660</v>
-      </c>
-      <c r="C289" t="s">
-        <v>661</v>
-      </c>
-      <c r="D289" t="s">
-        <v>661</v>
-      </c>
-      <c r="E289" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B290" t="s">
-        <v>662</v>
-      </c>
-      <c r="C290" t="s">
-        <v>663</v>
-      </c>
-      <c r="D290" t="s">
-        <v>663</v>
-      </c>
-      <c r="E290" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B291" t="s">
-        <v>664</v>
-      </c>
-      <c r="C291" t="s">
-        <v>665</v>
-      </c>
-      <c r="D291" t="s">
-        <v>665</v>
-      </c>
-      <c r="E291" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B292" t="s">
-        <v>666</v>
-      </c>
-      <c r="C292" t="s">
-        <v>667</v>
-      </c>
-      <c r="D292" t="s">
-        <v>667</v>
-      </c>
-      <c r="E292" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B293" t="s">
-        <v>668</v>
-      </c>
-      <c r="C293" t="s">
-        <v>669</v>
-      </c>
-      <c r="D293" t="s">
-        <v>669</v>
-      </c>
-      <c r="E293" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B294" t="s">
-        <v>670</v>
-      </c>
-      <c r="C294" t="s">
-        <v>671</v>
-      </c>
-      <c r="D294" t="s">
-        <v>671</v>
-      </c>
-      <c r="E294" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B295" t="s">
-        <v>672</v>
-      </c>
-      <c r="C295" t="s">
-        <v>673</v>
-      </c>
-      <c r="D295" t="s">
-        <v>673</v>
-      </c>
-      <c r="E295" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B296" t="s">
-        <v>674</v>
-      </c>
-      <c r="C296" t="s">
-        <v>675</v>
-      </c>
-      <c r="D296" t="s">
-        <v>675</v>
-      </c>
-      <c r="E296" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B297" t="s">
-        <v>676</v>
-      </c>
-      <c r="C297" t="s">
-        <v>677</v>
-      </c>
-      <c r="D297" t="s">
-        <v>677</v>
-      </c>
-      <c r="E297" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B298" t="s">
-        <v>678</v>
-      </c>
-      <c r="C298" t="s">
-        <v>679</v>
-      </c>
-      <c r="D298" t="s">
-        <v>679</v>
-      </c>
-      <c r="E298" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B299" t="s">
-        <v>680</v>
-      </c>
-      <c r="C299" t="s">
-        <v>681</v>
-      </c>
-      <c r="D299" t="s">
-        <v>681</v>
-      </c>
-      <c r="E299" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B300" t="s">
-        <v>682</v>
-      </c>
-      <c r="C300" t="s">
-        <v>683</v>
-      </c>
-      <c r="D300" t="s">
-        <v>683</v>
-      </c>
-      <c r="E300" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B301" t="s">
-        <v>684</v>
-      </c>
-      <c r="C301" t="s">
-        <v>685</v>
-      </c>
-      <c r="D301" t="s">
-        <v>685</v>
-      </c>
-      <c r="E301" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B302" t="s">
-        <v>686</v>
-      </c>
-      <c r="C302" t="s">
-        <v>687</v>
-      </c>
-      <c r="D302" t="s">
-        <v>687</v>
-      </c>
-      <c r="E302" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B303" t="s">
-        <v>688</v>
-      </c>
-      <c r="C303" t="s">
-        <v>689</v>
-      </c>
-      <c r="D303" t="s">
-        <v>689</v>
-      </c>
-      <c r="E303" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B304" t="s">
-        <v>690</v>
-      </c>
-      <c r="C304" t="s">
-        <v>691</v>
-      </c>
-      <c r="D304" t="s">
-        <v>691</v>
-      </c>
-      <c r="E304" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B305" t="s">
-        <v>692</v>
-      </c>
-      <c r="C305" t="s">
-        <v>693</v>
-      </c>
-      <c r="D305" t="s">
-        <v>693</v>
-      </c>
-      <c r="E305" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B306" t="s">
-        <v>694</v>
-      </c>
-      <c r="C306" t="s">
-        <v>695</v>
-      </c>
-      <c r="D306" t="s">
-        <v>695</v>
-      </c>
-      <c r="E306" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B307" t="s">
-        <v>696</v>
-      </c>
-      <c r="C307" t="s">
-        <v>697</v>
-      </c>
-      <c r="D307" t="s">
-        <v>697</v>
-      </c>
-      <c r="E307" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B308" t="s">
-        <v>698</v>
-      </c>
-      <c r="C308" t="s">
-        <v>699</v>
-      </c>
-      <c r="D308" t="s">
-        <v>699</v>
-      </c>
-      <c r="E308" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B309" t="s">
-        <v>700</v>
-      </c>
-      <c r="C309" t="s">
-        <v>701</v>
-      </c>
-      <c r="D309" t="s">
-        <v>701</v>
-      </c>
-      <c r="E309" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B310" t="s">
-        <v>702</v>
-      </c>
-      <c r="C310" t="s">
-        <v>703</v>
-      </c>
-      <c r="D310" t="s">
-        <v>703</v>
-      </c>
-      <c r="E310" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B311" t="s">
-        <v>704</v>
-      </c>
-      <c r="C311" t="s">
-        <v>705</v>
-      </c>
-      <c r="D311" t="s">
-        <v>705</v>
-      </c>
-      <c r="E311" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B312" t="s">
-        <v>706</v>
-      </c>
-      <c r="C312" t="s">
-        <v>707</v>
-      </c>
-      <c r="D312" t="s">
-        <v>707</v>
-      </c>
-      <c r="E312" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B313" t="s">
-        <v>708</v>
-      </c>
-      <c r="C313" t="s">
-        <v>709</v>
-      </c>
-      <c r="D313" t="s">
-        <v>709</v>
-      </c>
-      <c r="E313" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B314" t="s">
-        <v>710</v>
-      </c>
-      <c r="C314" t="s">
-        <v>711</v>
-      </c>
-      <c r="D314" t="s">
-        <v>711</v>
-      </c>
-      <c r="E314" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B315" t="s">
-        <v>712</v>
-      </c>
-      <c r="C315" t="s">
-        <v>713</v>
-      </c>
-      <c r="D315" t="s">
-        <v>713</v>
-      </c>
-      <c r="E315" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B316" t="s">
-        <v>714</v>
-      </c>
-      <c r="C316" t="s">
-        <v>715</v>
-      </c>
-      <c r="D316" t="s">
-        <v>715</v>
-      </c>
-      <c r="E316" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B317" t="s">
-        <v>716</v>
-      </c>
-      <c r="C317" t="s">
-        <v>717</v>
-      </c>
-      <c r="D317" t="s">
-        <v>717</v>
-      </c>
-      <c r="E317" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B318" t="s">
-        <v>718</v>
-      </c>
-      <c r="C318" t="s">
-        <v>719</v>
-      </c>
-      <c r="D318" t="s">
-        <v>719</v>
-      </c>
-      <c r="E318" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B319" t="s">
-        <v>720</v>
-      </c>
-      <c r="C319" t="s">
-        <v>721</v>
-      </c>
-      <c r="D319" t="s">
-        <v>721</v>
-      </c>
-      <c r="E319" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B320" t="s">
-        <v>722</v>
-      </c>
-      <c r="C320" t="s">
-        <v>723</v>
-      </c>
-      <c r="D320" t="s">
-        <v>723</v>
-      </c>
-      <c r="E320" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B321" t="s">
-        <v>724</v>
-      </c>
-      <c r="C321" t="s">
-        <v>725</v>
-      </c>
-      <c r="D321" t="s">
-        <v>725</v>
-      </c>
-      <c r="E321" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B322" t="s">
-        <v>726</v>
-      </c>
-      <c r="C322" t="s">
-        <v>727</v>
-      </c>
-      <c r="D322" t="s">
-        <v>727</v>
-      </c>
-      <c r="E322" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B323" t="s">
-        <v>728</v>
-      </c>
-      <c r="C323" t="s">
-        <v>729</v>
-      </c>
-      <c r="D323" t="s">
-        <v>729</v>
-      </c>
-      <c r="E323" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B324" t="s">
-        <v>730</v>
-      </c>
-      <c r="C324" t="s">
-        <v>731</v>
-      </c>
-      <c r="D324" t="s">
-        <v>731</v>
-      </c>
-      <c r="E324" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B325" t="s">
-        <v>732</v>
-      </c>
-      <c r="C325" t="s">
-        <v>733</v>
-      </c>
-      <c r="D325" t="s">
-        <v>733</v>
-      </c>
-      <c r="E325" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B326" t="s">
-        <v>734</v>
-      </c>
-      <c r="C326" t="s">
-        <v>735</v>
-      </c>
-      <c r="D326" t="s">
-        <v>735</v>
-      </c>
-      <c r="E326" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B327" t="s">
-        <v>736</v>
-      </c>
-      <c r="C327" t="s">
-        <v>737</v>
-      </c>
-      <c r="D327" t="s">
-        <v>737</v>
-      </c>
-      <c r="E327" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B328" t="s">
-        <v>738</v>
-      </c>
-      <c r="C328" t="s">
-        <v>739</v>
-      </c>
-      <c r="D328" t="s">
-        <v>739</v>
-      </c>
-      <c r="E328" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B329" t="s">
-        <v>740</v>
-      </c>
-      <c r="C329" t="s">
-        <v>741</v>
-      </c>
-      <c r="D329" t="s">
-        <v>741</v>
-      </c>
-      <c r="E329" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B330" t="s">
-        <v>742</v>
-      </c>
-      <c r="C330" t="s">
-        <v>743</v>
-      </c>
-      <c r="D330" t="s">
-        <v>743</v>
-      </c>
-      <c r="E330" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B331" t="s">
-        <v>744</v>
-      </c>
-      <c r="C331" t="s">
-        <v>745</v>
-      </c>
-      <c r="D331" t="s">
-        <v>745</v>
-      </c>
-      <c r="E331" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B332" t="s">
-        <v>746</v>
-      </c>
-      <c r="C332" t="s">
-        <v>747</v>
-      </c>
-      <c r="D332" t="s">
-        <v>747</v>
-      </c>
-      <c r="E332" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B333" t="s">
-        <v>748</v>
-      </c>
-      <c r="C333" t="s">
-        <v>749</v>
-      </c>
-      <c r="D333" t="s">
-        <v>749</v>
-      </c>
-      <c r="E333" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B334" t="s">
-        <v>750</v>
-      </c>
-      <c r="C334" t="s">
-        <v>751</v>
-      </c>
-      <c r="D334" t="s">
-        <v>751</v>
-      </c>
-      <c r="E334" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B335" t="s">
-        <v>752</v>
-      </c>
-      <c r="C335" t="s">
-        <v>753</v>
-      </c>
-      <c r="D335" t="s">
-        <v>753</v>
-      </c>
-      <c r="E335" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B336" t="s">
-        <v>754</v>
-      </c>
-      <c r="C336" t="s">
-        <v>755</v>
-      </c>
-      <c r="D336" t="s">
-        <v>755</v>
-      </c>
-      <c r="E336" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B337" t="s">
-        <v>756</v>
-      </c>
-      <c r="C337" t="s">
-        <v>757</v>
-      </c>
-      <c r="D337" t="s">
-        <v>757</v>
-      </c>
-      <c r="E337" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B338" t="s">
-        <v>758</v>
-      </c>
-      <c r="C338" t="s">
-        <v>759</v>
-      </c>
-      <c r="D338" t="s">
-        <v>759</v>
-      </c>
-      <c r="E338" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B339" t="s">
-        <v>760</v>
-      </c>
-      <c r="C339" t="s">
-        <v>761</v>
-      </c>
-      <c r="D339" t="s">
-        <v>761</v>
-      </c>
-      <c r="E339" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B340" t="s">
-        <v>762</v>
-      </c>
-      <c r="C340" t="s">
-        <v>763</v>
-      </c>
-      <c r="D340" t="s">
-        <v>763</v>
-      </c>
-      <c r="E340" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B341" t="s">
-        <v>764</v>
-      </c>
-      <c r="C341" t="s">
-        <v>765</v>
-      </c>
-      <c r="D341" t="s">
-        <v>765</v>
-      </c>
-      <c r="E341" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B342" t="s">
-        <v>766</v>
-      </c>
-      <c r="C342" t="s">
-        <v>767</v>
-      </c>
-      <c r="D342" t="s">
-        <v>767</v>
-      </c>
-      <c r="E342" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B343" t="s">
-        <v>768</v>
-      </c>
-      <c r="C343" t="s">
-        <v>769</v>
-      </c>
-      <c r="D343" t="s">
-        <v>769</v>
-      </c>
-      <c r="E343" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B344" t="s">
-        <v>770</v>
-      </c>
-      <c r="C344" t="s">
-        <v>771</v>
-      </c>
-      <c r="D344" t="s">
-        <v>771</v>
-      </c>
-      <c r="E344" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="345" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B345" t="s">
-        <v>772</v>
-      </c>
-      <c r="C345" t="s">
-        <v>773</v>
-      </c>
-      <c r="D345" t="s">
-        <v>773</v>
-      </c>
-      <c r="E345" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="346" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B346" t="s">
-        <v>774</v>
-      </c>
-      <c r="C346" t="s">
-        <v>775</v>
-      </c>
-      <c r="D346" t="s">
-        <v>775</v>
-      </c>
-      <c r="E346" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="347" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B347" t="s">
-        <v>776</v>
-      </c>
-      <c r="C347" t="s">
-        <v>777</v>
-      </c>
-      <c r="D347" t="s">
-        <v>777</v>
-      </c>
-      <c r="E347" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="348" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B348" t="s">
-        <v>778</v>
-      </c>
-      <c r="C348" t="s">
-        <v>779</v>
-      </c>
-      <c r="D348" t="s">
-        <v>779</v>
-      </c>
-      <c r="E348" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="349" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B349" t="s">
-        <v>780</v>
-      </c>
-      <c r="C349" t="s">
-        <v>781</v>
-      </c>
-      <c r="D349" t="s">
-        <v>781</v>
-      </c>
-      <c r="E349" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="350" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B350" t="s">
-        <v>782</v>
-      </c>
-      <c r="C350" t="s">
-        <v>783</v>
-      </c>
-      <c r="D350" t="s">
-        <v>783</v>
-      </c>
-      <c r="E350" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="351" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B351" t="s">
-        <v>784</v>
-      </c>
-      <c r="C351" t="s">
-        <v>785</v>
-      </c>
-      <c r="D351" t="s">
-        <v>785</v>
-      </c>
-      <c r="E351" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="352" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B352" t="s">
-        <v>786</v>
-      </c>
-      <c r="C352" t="s">
-        <v>787</v>
-      </c>
-      <c r="D352" t="s">
-        <v>787</v>
-      </c>
-      <c r="E352" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B353" t="s">
-        <v>788</v>
-      </c>
-      <c r="C353" t="s">
-        <v>789</v>
-      </c>
-      <c r="D353" t="s">
-        <v>789</v>
-      </c>
-      <c r="E353" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="354" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B354" t="s">
-        <v>790</v>
-      </c>
-      <c r="C354" t="s">
-        <v>791</v>
-      </c>
-      <c r="D354" t="s">
-        <v>791</v>
-      </c>
-      <c r="E354" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="355" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B355" t="s">
-        <v>792</v>
-      </c>
-      <c r="C355" t="s">
-        <v>793</v>
-      </c>
-      <c r="D355" t="s">
-        <v>793</v>
-      </c>
-      <c r="E355" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B356" t="s">
-        <v>794</v>
-      </c>
-      <c r="C356" t="s">
-        <v>795</v>
-      </c>
-      <c r="D356" t="s">
-        <v>795</v>
-      </c>
-      <c r="E356" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B357" t="s">
-        <v>796</v>
-      </c>
-      <c r="C357" t="s">
-        <v>797</v>
-      </c>
-      <c r="D357" t="s">
-        <v>797</v>
-      </c>
-      <c r="E357" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B358" t="s">
-        <v>798</v>
-      </c>
-      <c r="C358" t="s">
-        <v>799</v>
-      </c>
-      <c r="D358" t="s">
-        <v>799</v>
-      </c>
-      <c r="E358" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B359" t="s">
-        <v>800</v>
-      </c>
-      <c r="C359" t="s">
-        <v>801</v>
-      </c>
-      <c r="D359" t="s">
-        <v>801</v>
-      </c>
-      <c r="E359" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B360" t="s">
-        <v>802</v>
-      </c>
-      <c r="C360" t="s">
-        <v>803</v>
-      </c>
-      <c r="D360" t="s">
-        <v>803</v>
-      </c>
-      <c r="E360" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B361" t="s">
-        <v>804</v>
-      </c>
-      <c r="C361" t="s">
-        <v>805</v>
-      </c>
-      <c r="D361" t="s">
-        <v>805</v>
-      </c>
-      <c r="E361" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B362" t="s">
-        <v>806</v>
-      </c>
-      <c r="C362" t="s">
-        <v>807</v>
-      </c>
-      <c r="D362" t="s">
-        <v>807</v>
-      </c>
-      <c r="E362" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B363" t="s">
-        <v>808</v>
-      </c>
-      <c r="C363" t="s">
-        <v>809</v>
-      </c>
-      <c r="D363" t="s">
-        <v>809</v>
-      </c>
-      <c r="E363" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B364" t="s">
-        <v>810</v>
-      </c>
-      <c r="C364" t="s">
-        <v>811</v>
-      </c>
-      <c r="D364" t="s">
-        <v>811</v>
-      </c>
-      <c r="E364" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B365" t="s">
-        <v>812</v>
-      </c>
-      <c r="C365" t="s">
-        <v>813</v>
-      </c>
-      <c r="D365" t="s">
-        <v>813</v>
-      </c>
-      <c r="E365" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B366" t="s">
-        <v>814</v>
-      </c>
-      <c r="C366" t="s">
-        <v>815</v>
-      </c>
-      <c r="D366" t="s">
-        <v>815</v>
-      </c>
-      <c r="E366" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B367" t="s">
-        <v>816</v>
-      </c>
-      <c r="C367" t="s">
-        <v>817</v>
-      </c>
-      <c r="D367" t="s">
-        <v>817</v>
-      </c>
-      <c r="E367" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B368" t="s">
-        <v>818</v>
-      </c>
-      <c r="C368" t="s">
-        <v>819</v>
-      </c>
-      <c r="D368" t="s">
-        <v>819</v>
-      </c>
-      <c r="E368" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B369" t="s">
-        <v>820</v>
-      </c>
-      <c r="C369" t="s">
-        <v>821</v>
-      </c>
-      <c r="D369" t="s">
-        <v>821</v>
-      </c>
-      <c r="E369" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B370" t="s">
-        <v>822</v>
-      </c>
-      <c r="C370" t="s">
-        <v>823</v>
-      </c>
-      <c r="D370" t="s">
-        <v>823</v>
-      </c>
-      <c r="E370" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B371" t="s">
-        <v>824</v>
-      </c>
-      <c r="C371" t="s">
-        <v>825</v>
-      </c>
-      <c r="D371" t="s">
-        <v>825</v>
-      </c>
-      <c r="E371" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B372" t="s">
-        <v>826</v>
-      </c>
-      <c r="C372" t="s">
-        <v>827</v>
-      </c>
-      <c r="D372" t="s">
-        <v>827</v>
-      </c>
-      <c r="E372" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B373" t="s">
-        <v>828</v>
-      </c>
-      <c r="C373" t="s">
-        <v>829</v>
-      </c>
-      <c r="D373" t="s">
-        <v>829</v>
-      </c>
-      <c r="E373" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B374" t="s">
-        <v>830</v>
-      </c>
-      <c r="C374" t="s">
-        <v>831</v>
-      </c>
-      <c r="D374" t="s">
-        <v>831</v>
-      </c>
-      <c r="E374" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B375" t="s">
-        <v>832</v>
-      </c>
-      <c r="C375" t="s">
-        <v>833</v>
-      </c>
-      <c r="D375" t="s">
-        <v>833</v>
-      </c>
-      <c r="E375" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B376" t="s">
-        <v>834</v>
-      </c>
-      <c r="C376" t="s">
-        <v>835</v>
-      </c>
-      <c r="D376" t="s">
-        <v>835</v>
-      </c>
-      <c r="E376" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B377" t="s">
-        <v>836</v>
-      </c>
-      <c r="C377" t="s">
-        <v>837</v>
-      </c>
-      <c r="D377" t="s">
-        <v>837</v>
-      </c>
-      <c r="E377" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B378" t="s">
-        <v>838</v>
-      </c>
-      <c r="C378" t="s">
-        <v>839</v>
-      </c>
-      <c r="D378" t="s">
-        <v>839</v>
-      </c>
-      <c r="E378" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B379" t="s">
-        <v>840</v>
-      </c>
-      <c r="C379" t="s">
-        <v>841</v>
-      </c>
-      <c r="D379" t="s">
-        <v>841</v>
-      </c>
-      <c r="E379" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B380" t="s">
-        <v>842</v>
-      </c>
-      <c r="C380" t="s">
-        <v>843</v>
-      </c>
-      <c r="D380" t="s">
-        <v>843</v>
-      </c>
-      <c r="E380" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B381" t="s">
-        <v>844</v>
-      </c>
-      <c r="C381" t="s">
-        <v>845</v>
-      </c>
-      <c r="D381" t="s">
-        <v>845</v>
-      </c>
-      <c r="E381" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B382" t="s">
-        <v>846</v>
-      </c>
-      <c r="C382" t="s">
-        <v>847</v>
-      </c>
-      <c r="D382" t="s">
-        <v>847</v>
-      </c>
-      <c r="E382" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B383" t="s">
-        <v>848</v>
-      </c>
-      <c r="C383" t="s">
-        <v>849</v>
-      </c>
-      <c r="D383" t="s">
-        <v>849</v>
-      </c>
-      <c r="E383" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B384" t="s">
-        <v>850</v>
-      </c>
-      <c r="C384" t="s">
-        <v>851</v>
-      </c>
-      <c r="D384" t="s">
-        <v>851</v>
-      </c>
-      <c r="E384" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B385" t="s">
-        <v>852</v>
-      </c>
-      <c r="C385" t="s">
-        <v>853</v>
-      </c>
-      <c r="D385" t="s">
-        <v>853</v>
-      </c>
-      <c r="E385" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B386" t="s">
-        <v>854</v>
-      </c>
-      <c r="C386" t="s">
-        <v>855</v>
-      </c>
-      <c r="D386" t="s">
-        <v>855</v>
-      </c>
-      <c r="E386" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B387" t="s">
-        <v>856</v>
-      </c>
-      <c r="C387" t="s">
-        <v>857</v>
-      </c>
-      <c r="D387" t="s">
-        <v>857</v>
-      </c>
-      <c r="E387" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B388" t="s">
-        <v>858</v>
-      </c>
-      <c r="C388" t="s">
-        <v>859</v>
-      </c>
-      <c r="D388" t="s">
-        <v>859</v>
-      </c>
-      <c r="E388" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B389" t="s">
-        <v>860</v>
-      </c>
-      <c r="C389" t="s">
-        <v>861</v>
-      </c>
-      <c r="D389" t="s">
-        <v>861</v>
-      </c>
-      <c r="E389" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B390" t="s">
-        <v>862</v>
-      </c>
-      <c r="C390" t="s">
-        <v>863</v>
-      </c>
-      <c r="D390" t="s">
-        <v>863</v>
-      </c>
-      <c r="E390" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B391" t="s">
-        <v>864</v>
-      </c>
-      <c r="C391" t="s">
-        <v>865</v>
-      </c>
-      <c r="D391" t="s">
-        <v>865</v>
-      </c>
-      <c r="E391" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B392" t="s">
-        <v>866</v>
-      </c>
-      <c r="C392" t="s">
-        <v>867</v>
-      </c>
-      <c r="D392" t="s">
-        <v>867</v>
-      </c>
-      <c r="E392" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B393" t="s">
-        <v>868</v>
-      </c>
-      <c r="C393" t="s">
-        <v>869</v>
-      </c>
-      <c r="D393" t="s">
-        <v>869</v>
-      </c>
-      <c r="E393" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B394" t="s">
-        <v>870</v>
-      </c>
-      <c r="C394" t="s">
-        <v>871</v>
-      </c>
-      <c r="D394" t="s">
-        <v>871</v>
-      </c>
-      <c r="E394" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B395" t="s">
-        <v>872</v>
-      </c>
-      <c r="C395" t="s">
-        <v>873</v>
-      </c>
-      <c r="D395" t="s">
-        <v>873</v>
-      </c>
-      <c r="E395" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B396" t="s">
-        <v>874</v>
-      </c>
-      <c r="C396" t="s">
-        <v>875</v>
-      </c>
-      <c r="D396" t="s">
-        <v>875</v>
-      </c>
-      <c r="E396" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B397" t="s">
-        <v>876</v>
-      </c>
-      <c r="C397" t="s">
-        <v>877</v>
-      </c>
-      <c r="D397" t="s">
-        <v>877</v>
-      </c>
-      <c r="E397" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B398" t="s">
-        <v>878</v>
-      </c>
-      <c r="C398" t="s">
-        <v>879</v>
-      </c>
-      <c r="D398" t="s">
-        <v>879</v>
-      </c>
-      <c r="E398" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B399" t="s">
-        <v>880</v>
-      </c>
-      <c r="C399" t="s">
-        <v>881</v>
-      </c>
-      <c r="D399" t="s">
-        <v>881</v>
-      </c>
-      <c r="E399" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B400" t="s">
-        <v>882</v>
-      </c>
-      <c r="C400" t="s">
-        <v>883</v>
-      </c>
-      <c r="D400" t="s">
-        <v>883</v>
-      </c>
-      <c r="E400" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B401" t="s">
-        <v>884</v>
-      </c>
-      <c r="C401" t="s">
-        <v>885</v>
-      </c>
-      <c r="D401" t="s">
-        <v>885</v>
-      </c>
-      <c r="E401" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="402" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B402" t="s">
-        <v>886</v>
-      </c>
-      <c r="C402" t="s">
-        <v>887</v>
-      </c>
-      <c r="D402" t="s">
-        <v>887</v>
-      </c>
-      <c r="E402" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="403" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B403" t="s">
-        <v>888</v>
-      </c>
-      <c r="C403" t="s">
-        <v>889</v>
-      </c>
-      <c r="D403" t="s">
-        <v>889</v>
-      </c>
-      <c r="E403" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="404" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B404" t="s">
-        <v>890</v>
-      </c>
-      <c r="C404" t="s">
-        <v>891</v>
-      </c>
-      <c r="D404" t="s">
-        <v>891</v>
-      </c>
-      <c r="E404" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="405" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B405" t="s">
-        <v>892</v>
-      </c>
-      <c r="C405" t="s">
-        <v>893</v>
-      </c>
-      <c r="D405" t="s">
-        <v>893</v>
-      </c>
-      <c r="E405" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B406" t="s">
-        <v>894</v>
-      </c>
-      <c r="C406" t="s">
-        <v>895</v>
-      </c>
-      <c r="D406" t="s">
-        <v>895</v>
-      </c>
-      <c r="E406" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B407" t="s">
-        <v>896</v>
-      </c>
-      <c r="C407" t="s">
-        <v>897</v>
-      </c>
-      <c r="D407" t="s">
-        <v>897</v>
-      </c>
-      <c r="E407" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="408" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B408" t="s">
-        <v>898</v>
-      </c>
-      <c r="C408" t="s">
-        <v>899</v>
-      </c>
-      <c r="D408" t="s">
-        <v>899</v>
-      </c>
-      <c r="E408" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="409" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B409" t="s">
-        <v>900</v>
-      </c>
-      <c r="C409" t="s">
-        <v>901</v>
-      </c>
-      <c r="D409" t="s">
-        <v>901</v>
-      </c>
-      <c r="E409" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="410" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B410" t="s">
-        <v>902</v>
-      </c>
-      <c r="C410" t="s">
-        <v>903</v>
-      </c>
-      <c r="D410" t="s">
-        <v>903</v>
-      </c>
-      <c r="E410" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="411" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B411" t="s">
-        <v>904</v>
-      </c>
-      <c r="C411" t="s">
-        <v>905</v>
-      </c>
-      <c r="D411" t="s">
-        <v>905</v>
-      </c>
-      <c r="E411" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="412" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B412" t="s">
-        <v>906</v>
-      </c>
-      <c r="C412" t="s">
-        <v>907</v>
-      </c>
-      <c r="D412" t="s">
-        <v>907</v>
-      </c>
-      <c r="E412" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="413" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B413" t="s">
-        <v>908</v>
-      </c>
-      <c r="C413" t="s">
-        <v>909</v>
-      </c>
-      <c r="D413" t="s">
-        <v>909</v>
-      </c>
-      <c r="E413" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B414" t="s">
-        <v>910</v>
-      </c>
-      <c r="C414" t="s">
-        <v>911</v>
-      </c>
-      <c r="D414" t="s">
-        <v>911</v>
-      </c>
-      <c r="E414" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B415" t="s">
-        <v>912</v>
-      </c>
-      <c r="C415" t="s">
-        <v>913</v>
-      </c>
-      <c r="D415" t="s">
-        <v>913</v>
-      </c>
-      <c r="E415" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B416" t="s">
-        <v>914</v>
-      </c>
-      <c r="C416" t="s">
-        <v>915</v>
-      </c>
-      <c r="D416" t="s">
-        <v>915</v>
-      </c>
-      <c r="E416" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B417" t="s">
-        <v>916</v>
-      </c>
-      <c r="C417" t="s">
-        <v>917</v>
-      </c>
-      <c r="D417" t="s">
-        <v>917</v>
-      </c>
-      <c r="E417" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B418" t="s">
-        <v>918</v>
-      </c>
-      <c r="C418" t="s">
-        <v>919</v>
-      </c>
-      <c r="D418" t="s">
-        <v>919</v>
-      </c>
-      <c r="E418" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B419" t="s">
-        <v>920</v>
-      </c>
-      <c r="C419" t="s">
-        <v>921</v>
-      </c>
-      <c r="D419" t="s">
-        <v>921</v>
-      </c>
-      <c r="E419" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B420" t="s">
-        <v>922</v>
-      </c>
-      <c r="C420" t="s">
-        <v>923</v>
-      </c>
-      <c r="D420" t="s">
-        <v>923</v>
-      </c>
-      <c r="E420" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B421" t="s">
-        <v>924</v>
-      </c>
-      <c r="C421" t="s">
-        <v>925</v>
-      </c>
-      <c r="D421" t="s">
-        <v>925</v>
-      </c>
-      <c r="E421" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="422" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B422" t="s">
-        <v>926</v>
-      </c>
-      <c r="C422" t="s">
-        <v>927</v>
-      </c>
-      <c r="D422" t="s">
-        <v>927</v>
-      </c>
-      <c r="E422" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="423" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B423" t="s">
-        <v>928</v>
-      </c>
-      <c r="C423" t="s">
-        <v>929</v>
-      </c>
-      <c r="D423" t="s">
-        <v>929</v>
-      </c>
-      <c r="E423" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="424" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B424" t="s">
-        <v>930</v>
-      </c>
-      <c r="C424" t="s">
-        <v>931</v>
-      </c>
-      <c r="D424" t="s">
-        <v>931</v>
-      </c>
-      <c r="E424" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="425" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B425" t="s">
-        <v>932</v>
-      </c>
-      <c r="C425" t="s">
-        <v>933</v>
-      </c>
-      <c r="D425" t="s">
-        <v>933</v>
-      </c>
-      <c r="E425" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="426" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B426" t="s">
-        <v>934</v>
-      </c>
-      <c r="C426" t="s">
-        <v>935</v>
-      </c>
-      <c r="D426" t="s">
-        <v>935</v>
-      </c>
-      <c r="E426" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="427" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B427" t="s">
-        <v>936</v>
-      </c>
-      <c r="C427" t="s">
-        <v>937</v>
-      </c>
-      <c r="D427" t="s">
-        <v>937</v>
-      </c>
-      <c r="E427" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="428" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B428" t="s">
-        <v>938</v>
-      </c>
-      <c r="C428" t="s">
-        <v>939</v>
-      </c>
-      <c r="D428" t="s">
-        <v>939</v>
-      </c>
-      <c r="E428" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="429" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B429" t="s">
-        <v>940</v>
-      </c>
-      <c r="C429" t="s">
-        <v>941</v>
-      </c>
-      <c r="D429" t="s">
-        <v>941</v>
-      </c>
-      <c r="E429" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="430" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B430" t="s">
-        <v>942</v>
-      </c>
-      <c r="C430" t="s">
-        <v>943</v>
-      </c>
-      <c r="D430" t="s">
-        <v>943</v>
-      </c>
-      <c r="E430" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="431" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B431" t="s">
-        <v>944</v>
-      </c>
-      <c r="C431" t="s">
-        <v>945</v>
-      </c>
-      <c r="D431" t="s">
-        <v>945</v>
-      </c>
-      <c r="E431" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="432" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B432" t="s">
-        <v>946</v>
-      </c>
-      <c r="C432" t="s">
-        <v>947</v>
-      </c>
-      <c r="D432" t="s">
-        <v>947</v>
-      </c>
-      <c r="E432" t="s">
         <v>105</v>
       </c>
     </row>

--- a/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4192FBC4-3BB0-4BF9-9EDF-5AD7A54ED161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7F2C3D7-DC51-4498-81E8-4F0E5A881563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2315,7 +2315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013E078F-6DD0-42C2-86A0-920142156F6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F022F03-9208-4B44-879D-4E1F5724AB4E}">
   <dimension ref="B9:E198"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_DZA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7F2C3D7-DC51-4498-81E8-4F0E5A881563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{482E439A-5A06-41F1-9448-E74C572FC8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2315,7 +2315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F022F03-9208-4B44-879D-4E1F5724AB4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D77C16F-B2E2-47BE-93D1-18291BABEA2C}">
   <dimension ref="B9:E198"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
